--- a/incident_report_forms/036_emergency_evacuation_assistance_request--incident_report_forms.xlsx
+++ b/incident_report_forms/036_emergency_evacuation_assistance_request--incident_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -761,8 +761,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -790,12 +790,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'evacuation',_'value':_'evacuation'}</t>
+          <t>evacuation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Evacuation', 'value': 'Evacuation'}</t>
+          <t>Evacuation</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'evacuation_due_to_weather',_'value':_'evacuation_due_to_weather'}</t>
+          <t>evacuation_due_to_weather</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Evacuation due to weather', 'value': 'Evacuation due to weather'}</t>
+          <t>Evacuation due to weather</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'emergency_assistance',_'value':_'emergency_assistance'}</t>
+          <t>emergency_assistance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Emergency assistance', 'value': 'Emergency assistance'}</t>
+          <t>Emergency assistance</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'transportation',_'value':_'transportation'}</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Transportation', 'value': 'Transportation'}</t>
+          <t>Transportation</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'shelter',_'value':_'shelter'}</t>
+          <t>shelter</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Shelter', 'value': 'Shelter'}</t>
+          <t>Shelter</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'food',_'value':_'food'}</t>
+          <t>food</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Food', 'value': 'Food'}</t>
+          <t>Food</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'clothing',_'value':_'clothing'}</t>
+          <t>clothing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Clothing', 'value': 'Clothing'}</t>
+          <t>Clothing</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
